--- a/playground/public/bd-prepare-template.xlsx
+++ b/playground/public/bd-prepare-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wei/work/shop_system/system_code/mis/playground/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wei/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E3FE22-DFDE-8348-8F8D-C7C7BFEEC4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8997AFE9-1049-EF46-8D18-5B03D922854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8900" yWindow="12160" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="达人筹备" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,160 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>kol_id</t>
   </si>
   <si>
     <t>KOL_TT_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_0010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_039</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOL_TT_041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kol_link</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -413,25 +561,203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
